--- a/services_forms/006_inspection_registration_form--services_forms.xlsx
+++ b/services_forms/006_inspection_registration_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'$0-$500',_'value':_'$0-$500'}</t>
+          <t>$0-$500</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '$0-$500', 'value': '$0-$500'}</t>
+          <t>$0-$500</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'$500-$1000',_'value':_'$500-$1000'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '$500-$1000', 'value': '$500-$1000'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'$1000-$2000',_'value':_'$1000-$2000'}</t>
+          <t>$1000-$2000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '$1000-$2000', 'value': '$1000-$2000'}</t>
+          <t>$1000-$2000</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'more_than_$2000',_'value':_'more_than_$2000'}</t>
+          <t>more_than_$2000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'more than $2000', 'value': 'more than $2000'}</t>
+          <t>more than $2000</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'admin',_'value':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'admin', 'value': 'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'manager', 'value': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'team',_'value':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'team', 'value': 'team'}</t>
+          <t>team</t>
         </is>
       </c>
     </row>
